--- a/data/nzd0041/nzd0041.xlsx
+++ b/data/nzd0041/nzd0041.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K479"/>
+  <dimension ref="A1:K481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19125,6 +19125,84 @@
         <v>381.7</v>
       </c>
       <c r="K479" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="C480" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="D480" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="E480" t="n">
+        <v>367.79</v>
+      </c>
+      <c r="F480" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="G480" t="n">
+        <v>377.42</v>
+      </c>
+      <c r="H480" t="n">
+        <v>374.02</v>
+      </c>
+      <c r="I480" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="J480" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>378.41</v>
+      </c>
+      <c r="C481" t="n">
+        <v>374.08</v>
+      </c>
+      <c r="D481" t="n">
+        <v>364.77</v>
+      </c>
+      <c r="E481" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="F481" t="n">
+        <v>370.53</v>
+      </c>
+      <c r="G481" t="n">
+        <v>378.07</v>
+      </c>
+      <c r="H481" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="I481" t="n">
+        <v>375.27</v>
+      </c>
+      <c r="J481" t="n">
+        <v>382.55</v>
+      </c>
+      <c r="K481" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19141,7 +19219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24874,6 +24952,26 @@
       </c>
       <c r="B573" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -25042,28 +25140,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5569496962185528</v>
+        <v>0.5474300877902419</v>
       </c>
       <c r="J2" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1995349492945911</v>
+        <v>0.1940495297919504</v>
       </c>
       <c r="M2" t="n">
-        <v>6.707613612919043</v>
+        <v>6.721580294741604</v>
       </c>
       <c r="N2" t="n">
-        <v>75.42572617293962</v>
+        <v>75.76467820697756</v>
       </c>
       <c r="O2" t="n">
-        <v>8.68479856835722</v>
+        <v>8.704290792877819</v>
       </c>
       <c r="P2" t="n">
-        <v>375.6601881611712</v>
+        <v>375.7529661484739</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25120,28 +25218,28 @@
         <v>0.1183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2539412765925682</v>
+        <v>0.2530737560067409</v>
       </c>
       <c r="J3" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K3" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2474837209265734</v>
+        <v>0.2476892208490944</v>
       </c>
       <c r="M3" t="n">
-        <v>2.692982121379096</v>
+        <v>2.686436935641046</v>
       </c>
       <c r="N3" t="n">
-        <v>11.88502273528324</v>
+        <v>11.84126490328987</v>
       </c>
       <c r="O3" t="n">
-        <v>3.447466132579585</v>
+        <v>3.441113904434125</v>
       </c>
       <c r="P3" t="n">
-        <v>368.256800607665</v>
+        <v>368.2652553341928</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25198,28 +25296,28 @@
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2517544459595813</v>
+        <v>0.249096361641626</v>
       </c>
       <c r="J4" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K4" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1977860679321158</v>
+        <v>0.1952483739818084</v>
       </c>
       <c r="M4" t="n">
-        <v>3.039266372398836</v>
+        <v>3.041522283685793</v>
       </c>
       <c r="N4" t="n">
-        <v>15.58163255968968</v>
+        <v>15.56764442293042</v>
       </c>
       <c r="O4" t="n">
-        <v>3.947357668072362</v>
+        <v>3.945585434752418</v>
       </c>
       <c r="P4" t="n">
-        <v>361.4710459711899</v>
+        <v>361.4969516263059</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25276,28 +25374,28 @@
         <v>0.1474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2881483716132527</v>
+        <v>0.286443757716816</v>
       </c>
       <c r="J5" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K5" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2794986844125327</v>
+        <v>0.278482006824966</v>
       </c>
       <c r="M5" t="n">
-        <v>2.81516048314628</v>
+        <v>2.812129129240511</v>
       </c>
       <c r="N5" t="n">
-        <v>12.97333124151919</v>
+        <v>12.94024350445819</v>
       </c>
       <c r="O5" t="n">
-        <v>3.601851085416941</v>
+        <v>3.59725499575137</v>
       </c>
       <c r="P5" t="n">
-        <v>362.6029180847046</v>
+        <v>362.619531220134</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25354,28 +25452,28 @@
         <v>0.1387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2483389405800013</v>
+        <v>0.2450087540937266</v>
       </c>
       <c r="J6" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K6" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1683279529917368</v>
+        <v>0.1651461531797799</v>
       </c>
       <c r="M6" t="n">
-        <v>3.272474008539158</v>
+        <v>3.27586008092525</v>
       </c>
       <c r="N6" t="n">
-        <v>18.46926736907502</v>
+        <v>18.47221149811995</v>
       </c>
       <c r="O6" t="n">
-        <v>4.297588552790392</v>
+        <v>4.297931071820481</v>
       </c>
       <c r="P6" t="n">
-        <v>368.1866799767334</v>
+        <v>368.2191359444646</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25432,28 +25530,28 @@
         <v>0.1225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1980033366525186</v>
+        <v>0.1952720354335904</v>
       </c>
       <c r="J7" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K7" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1223321174903461</v>
+        <v>0.1199341392818716</v>
       </c>
       <c r="M7" t="n">
-        <v>2.966615043572893</v>
+        <v>2.968926009562699</v>
       </c>
       <c r="N7" t="n">
-        <v>17.04899910604871</v>
+        <v>17.03201990228079</v>
       </c>
       <c r="O7" t="n">
-        <v>4.129043364515407</v>
+        <v>4.126986782421382</v>
       </c>
       <c r="P7" t="n">
-        <v>376.1460129840085</v>
+        <v>376.1726321445332</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25510,28 +25608,28 @@
         <v>0.1273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1989448799844329</v>
+        <v>0.1918708018924005</v>
       </c>
       <c r="J8" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K8" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09188498440787984</v>
+        <v>0.08549418415684473</v>
       </c>
       <c r="M8" t="n">
-        <v>3.83708911069444</v>
+        <v>3.857934080927108</v>
       </c>
       <c r="N8" t="n">
-        <v>23.70969687475705</v>
+        <v>23.9707365386869</v>
       </c>
       <c r="O8" t="n">
-        <v>4.869260403260134</v>
+        <v>4.895991885071594</v>
       </c>
       <c r="P8" t="n">
-        <v>378.337513202309</v>
+        <v>378.4064572348504</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25588,28 +25686,28 @@
         <v>0.0502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08153201060908245</v>
+        <v>0.07683238249240976</v>
       </c>
       <c r="J9" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K9" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0206216607946641</v>
+        <v>0.01835746077523215</v>
       </c>
       <c r="M9" t="n">
-        <v>3.442862553928729</v>
+        <v>3.453254308294491</v>
       </c>
       <c r="N9" t="n">
-        <v>19.13583060140816</v>
+        <v>19.2151181883555</v>
       </c>
       <c r="O9" t="n">
-        <v>4.374452034416215</v>
+        <v>4.383505239914228</v>
       </c>
       <c r="P9" t="n">
-        <v>379.0760918778464</v>
+        <v>379.1218944339225</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25666,28 +25764,28 @@
         <v>0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1035287574132818</v>
+        <v>0.1002298725230191</v>
       </c>
       <c r="J10" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K10" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04988744083815699</v>
+        <v>0.04699958146554728</v>
       </c>
       <c r="M10" t="n">
-        <v>2.859024082286169</v>
+        <v>2.864608397102507</v>
       </c>
       <c r="N10" t="n">
-        <v>12.37285700042929</v>
+        <v>12.39958513592864</v>
       </c>
       <c r="O10" t="n">
-        <v>3.517507213983973</v>
+        <v>3.521304465099353</v>
       </c>
       <c r="P10" t="n">
-        <v>384.0598606537138</v>
+        <v>384.0920116006457</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25725,7 +25823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K479"/>
+  <dimension ref="A1:K481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53031,6 +53129,120 @@
         </is>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>-34.98904694164378,173.47984602671914</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>-34.98949771498341,173.48050666884694</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>-34.98967542989047,173.48134818952533</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-34.98980167435134,173.48223502424563</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-34.99003600445819,173.48308750945904</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>-34.990173523097894,173.48395777394106</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>-34.9902971890498,173.48482172816253</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-34.99028020190835,173.4857184355698</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>-34.99029742861785,173.48661837508803</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>-34.98903713380042,173.47985497234674</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>-34.98949287875592,173.480509088073</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>-34.9896720553816,173.48134891244712</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-34.98979924789843,173.48223587229626</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>-34.990032316628934,173.48308896470013</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>-34.990167782325166,173.4839592102963</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>-34.990293497580396,173.4848219752972</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-34.99027551826385,173.48571870688454</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>-34.99029518873862,173.48661868453237</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0041/nzd0041.xlsx
+++ b/data/nzd0041/nzd0041.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K481"/>
+  <dimension ref="A1:K484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19203,6 +19203,123 @@
         <v>382.55</v>
       </c>
       <c r="K481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>372.42</v>
+      </c>
+      <c r="C482" t="n">
+        <v>371.49</v>
+      </c>
+      <c r="D482" t="n">
+        <v>362.82</v>
+      </c>
+      <c r="E482" t="n">
+        <v>366.26</v>
+      </c>
+      <c r="F482" t="n">
+        <v>369.25</v>
+      </c>
+      <c r="G482" t="n">
+        <v>376.56</v>
+      </c>
+      <c r="H482" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="I482" t="n">
+        <v>372.73</v>
+      </c>
+      <c r="J482" t="n">
+        <v>380.04</v>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>373.57</v>
+      </c>
+      <c r="C483" t="n">
+        <v>372.59</v>
+      </c>
+      <c r="D483" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="E483" t="n">
+        <v>367.14</v>
+      </c>
+      <c r="F483" t="n">
+        <v>369.87</v>
+      </c>
+      <c r="G483" t="n">
+        <v>377.72</v>
+      </c>
+      <c r="H483" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="I483" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="J483" t="n">
+        <v>381.03</v>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>373.93</v>
+      </c>
+      <c r="C484" t="n">
+        <v>372.21</v>
+      </c>
+      <c r="D484" t="n">
+        <v>363.47</v>
+      </c>
+      <c r="E484" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="F484" t="n">
+        <v>369.83</v>
+      </c>
+      <c r="G484" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="H484" t="n">
+        <v>374.55</v>
+      </c>
+      <c r="I484" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="J484" t="n">
+        <v>380.41</v>
+      </c>
+      <c r="K484" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19219,7 +19336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B575"/>
+  <dimension ref="A1:B578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24972,6 +25089,36 @@
       </c>
       <c r="B575" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -25140,28 +25287,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5474300877902419</v>
+        <v>0.528446731546879</v>
       </c>
       <c r="J2" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K2" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1940495297919504</v>
+        <v>0.1817137234728046</v>
       </c>
       <c r="M2" t="n">
-        <v>6.721580294741604</v>
+        <v>6.764285070833534</v>
       </c>
       <c r="N2" t="n">
-        <v>75.76467820697756</v>
+        <v>77.037394245819</v>
       </c>
       <c r="O2" t="n">
-        <v>8.704290792877819</v>
+        <v>8.777094863667534</v>
       </c>
       <c r="P2" t="n">
-        <v>375.7529661484739</v>
+        <v>375.9388637022467</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25218,28 +25365,28 @@
         <v>0.1183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2530737560067409</v>
+        <v>0.2498708787650755</v>
       </c>
       <c r="J3" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K3" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2476892208490944</v>
+        <v>0.2445016727836542</v>
       </c>
       <c r="M3" t="n">
-        <v>2.686436935641046</v>
+        <v>2.686791803496629</v>
       </c>
       <c r="N3" t="n">
-        <v>11.84126490328987</v>
+        <v>11.81856023110386</v>
       </c>
       <c r="O3" t="n">
-        <v>3.441113904434125</v>
+        <v>3.437813292065737</v>
       </c>
       <c r="P3" t="n">
-        <v>368.2652553341928</v>
+        <v>368.2966178692936</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25296,28 +25443,28 @@
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.249096361641626</v>
+        <v>0.2437030674223246</v>
       </c>
       <c r="J4" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K4" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1952483739818084</v>
+        <v>0.1890006040952027</v>
       </c>
       <c r="M4" t="n">
-        <v>3.041522283685793</v>
+        <v>3.052848508501147</v>
       </c>
       <c r="N4" t="n">
-        <v>15.56764442293042</v>
+        <v>15.61208624298475</v>
       </c>
       <c r="O4" t="n">
-        <v>3.945585434752418</v>
+        <v>3.95121326214933</v>
       </c>
       <c r="P4" t="n">
-        <v>361.4969516263059</v>
+        <v>361.5497652362758</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25374,28 +25521,28 @@
         <v>0.1474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.286443757716816</v>
+        <v>0.2825486029631489</v>
       </c>
       <c r="J5" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K5" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L5" t="n">
-        <v>0.278482006824966</v>
+        <v>0.2743768548042071</v>
       </c>
       <c r="M5" t="n">
-        <v>2.812129129240511</v>
+        <v>2.814463180057571</v>
       </c>
       <c r="N5" t="n">
-        <v>12.94024350445819</v>
+        <v>12.93396240598429</v>
       </c>
       <c r="O5" t="n">
-        <v>3.59725499575137</v>
+        <v>3.596381849301362</v>
       </c>
       <c r="P5" t="n">
-        <v>362.619531220134</v>
+        <v>362.6576747912341</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25452,28 +25599,28 @@
         <v>0.1387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2450087540937266</v>
+        <v>0.2393471115914567</v>
       </c>
       <c r="J6" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K6" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1651461531797799</v>
+        <v>0.1593589336126132</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27586008092525</v>
+        <v>3.284224398867409</v>
       </c>
       <c r="N6" t="n">
-        <v>18.47221149811995</v>
+        <v>18.51280305374333</v>
       </c>
       <c r="O6" t="n">
-        <v>4.297931071820481</v>
+        <v>4.302650700875372</v>
       </c>
       <c r="P6" t="n">
-        <v>368.2191359444646</v>
+        <v>368.2745779582946</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25530,28 +25677,28 @@
         <v>0.1225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1952720354335904</v>
+        <v>0.1902282798692702</v>
       </c>
       <c r="J7" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K7" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1199341392818716</v>
+        <v>0.1150497380048895</v>
       </c>
       <c r="M7" t="n">
-        <v>2.968926009562699</v>
+        <v>2.978087633010651</v>
       </c>
       <c r="N7" t="n">
-        <v>17.03201990228079</v>
+        <v>17.05159472561903</v>
       </c>
       <c r="O7" t="n">
-        <v>4.126986782421382</v>
+        <v>4.129357665015109</v>
       </c>
       <c r="P7" t="n">
-        <v>376.1726321445332</v>
+        <v>376.2220300229437</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25608,28 +25755,28 @@
         <v>0.1273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1918708018924005</v>
+        <v>0.1814396168162645</v>
       </c>
       <c r="J8" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K8" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08549418415684473</v>
+        <v>0.07649164601750369</v>
       </c>
       <c r="M8" t="n">
-        <v>3.857934080927108</v>
+        <v>3.887716276780156</v>
       </c>
       <c r="N8" t="n">
-        <v>23.9707365386869</v>
+        <v>24.34852593291164</v>
       </c>
       <c r="O8" t="n">
-        <v>4.895991885071594</v>
+        <v>4.934422553137463</v>
       </c>
       <c r="P8" t="n">
-        <v>378.4064572348504</v>
+        <v>378.5086056559221</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25686,28 +25833,28 @@
         <v>0.0502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07683238249240976</v>
+        <v>0.06814798141575255</v>
       </c>
       <c r="J9" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K9" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01835746077523215</v>
+        <v>0.01440770584075357</v>
       </c>
       <c r="M9" t="n">
-        <v>3.453254308294491</v>
+        <v>3.477773943396614</v>
       </c>
       <c r="N9" t="n">
-        <v>19.2151181883555</v>
+        <v>19.46211664146666</v>
       </c>
       <c r="O9" t="n">
-        <v>4.383505239914228</v>
+        <v>4.411588902137942</v>
       </c>
       <c r="P9" t="n">
-        <v>379.1218944339225</v>
+        <v>379.2069331169097</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25764,28 +25911,28 @@
         <v>0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1002298725230191</v>
+        <v>0.09321711027978943</v>
       </c>
       <c r="J10" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K10" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04699958146554728</v>
+        <v>0.04065534825754047</v>
       </c>
       <c r="M10" t="n">
-        <v>2.864608397102507</v>
+        <v>2.884278869600076</v>
       </c>
       <c r="N10" t="n">
-        <v>12.39958513592864</v>
+        <v>12.5611631579243</v>
       </c>
       <c r="O10" t="n">
-        <v>3.521304465099353</v>
+        <v>3.544173127532613</v>
       </c>
       <c r="P10" t="n">
-        <v>384.0920116006457</v>
+        <v>384.1606870926161</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25823,7 +25970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K481"/>
+  <dimension ref="A1:K484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53243,6 +53390,177 @@
         </is>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>-34.989080331576126,173.4798155721033</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>-34.98951447501273,173.48049828497523</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>-34.9896893719402,173.4813452027164</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-34.98981493318327,173.48223039025376</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>-34.9900432943532,173.48308463281927</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>-34.99018111858179,173.4839558735323</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-34.990300880519214,173.4848214810278</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-34.99029839606576,173.48571738161613</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>-34.99031767712601,173.48661557771067</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>-34.989072038181114,173.47982313642703</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>-34.98950530285747,173.48050287316414</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>-34.9896831557397,173.48134653441477</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-34.989807307188464,173.48223305555646</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>-34.990037977018034,173.48308673107422</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>-34.99017087351049,173.48395843687427</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-34.99029376768791,173.4848219572142</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-34.9902922712999,173.48571773641245</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>-34.99030880720431,173.48661680311065</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>-34.9890694419878,173.47982550438894</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>-34.989508471420216,173.48050128815353</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>-34.989683599754024,173.48134643929345</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-34.98981077354975,173.48223184405532</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>-34.99003832007191,173.48308659570293</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>-34.99018394480835,173.48395516640335</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-34.99029241715032,173.4848220476293</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-34.99028596639387,173.48571810164393</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>-34.990314362104776,173.48661603568846</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0041/nzd0041.xlsx
+++ b/data/nzd0041/nzd0041.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K484"/>
+  <dimension ref="A1:K485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19322,6 +19322,45 @@
       <c r="K484" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>377.22</v>
+      </c>
+      <c r="C485" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="D485" t="n">
+        <v>364.72</v>
+      </c>
+      <c r="E485" t="n">
+        <v>366.79</v>
+      </c>
+      <c r="F485" t="n">
+        <v>371.88</v>
+      </c>
+      <c r="G485" t="n">
+        <v>376.59</v>
+      </c>
+      <c r="H485" t="n">
+        <v>375.72</v>
+      </c>
+      <c r="I485" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="J485" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19336,7 +19375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B578"/>
+  <dimension ref="A1:B579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25119,6 +25158,16 @@
       </c>
       <c r="B578" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -25287,28 +25336,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.528446731546879</v>
+        <v>0.5236389880995698</v>
       </c>
       <c r="J2" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K2" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1817137234728046</v>
+        <v>0.1789981735538143</v>
       </c>
       <c r="M2" t="n">
-        <v>6.764285070833534</v>
+        <v>6.772198383156253</v>
       </c>
       <c r="N2" t="n">
-        <v>77.037394245819</v>
+        <v>77.21205385669964</v>
       </c>
       <c r="O2" t="n">
-        <v>8.777094863667534</v>
+        <v>8.787038969795208</v>
       </c>
       <c r="P2" t="n">
-        <v>375.9388637022467</v>
+        <v>375.9862944480294</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25365,28 +25414,28 @@
         <v>0.1183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2498708787650755</v>
+        <v>0.249068652317975</v>
       </c>
       <c r="J3" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K3" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2445016727836542</v>
+        <v>0.2439521253752939</v>
       </c>
       <c r="M3" t="n">
-        <v>2.686791803496629</v>
+        <v>2.685463413385588</v>
       </c>
       <c r="N3" t="n">
-        <v>11.81856023110386</v>
+        <v>11.80343638569793</v>
       </c>
       <c r="O3" t="n">
-        <v>3.437813292065737</v>
+        <v>3.435612956329325</v>
       </c>
       <c r="P3" t="n">
-        <v>368.2966178692936</v>
+        <v>368.3045322264322</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25443,28 +25492,28 @@
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2437030674223246</v>
+        <v>0.2424592457364116</v>
       </c>
       <c r="J4" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K4" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1890006040952027</v>
+        <v>0.1878651317543121</v>
       </c>
       <c r="M4" t="n">
-        <v>3.052848508501147</v>
+        <v>3.05354725261306</v>
       </c>
       <c r="N4" t="n">
-        <v>15.61208624298475</v>
+        <v>15.60217362115848</v>
       </c>
       <c r="O4" t="n">
-        <v>3.95121326214933</v>
+        <v>3.949958686006536</v>
       </c>
       <c r="P4" t="n">
-        <v>361.5497652362758</v>
+        <v>361.5620361469078</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25521,28 +25570,28 @@
         <v>0.1474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2825486029631489</v>
+        <v>0.281279369126937</v>
       </c>
       <c r="J5" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K5" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2743768548042071</v>
+        <v>0.27307205283892</v>
       </c>
       <c r="M5" t="n">
-        <v>2.814463180057571</v>
+        <v>2.81516338471639</v>
       </c>
       <c r="N5" t="n">
-        <v>12.93396240598429</v>
+        <v>12.930505421649</v>
       </c>
       <c r="O5" t="n">
-        <v>3.596381849301362</v>
+        <v>3.595901197425897</v>
       </c>
       <c r="P5" t="n">
-        <v>362.6576747912341</v>
+        <v>362.6701964051854</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25599,28 +25648,28 @@
         <v>0.1387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2393471115914567</v>
+        <v>0.2383116614697237</v>
       </c>
       <c r="J6" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K6" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1593589336126132</v>
+        <v>0.158654622373804</v>
       </c>
       <c r="M6" t="n">
-        <v>3.284224398867409</v>
+        <v>3.282622914007482</v>
       </c>
       <c r="N6" t="n">
-        <v>18.51280305374333</v>
+        <v>18.49003799940491</v>
       </c>
       <c r="O6" t="n">
-        <v>4.302650700875372</v>
+        <v>4.300004418533184</v>
       </c>
       <c r="P6" t="n">
-        <v>368.2745779582946</v>
+        <v>368.2847931813058</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25677,28 +25726,28 @@
         <v>0.1225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1902282798692702</v>
+        <v>0.188462490367517</v>
       </c>
       <c r="J7" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K7" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1150497380048895</v>
+        <v>0.1133249214415187</v>
       </c>
       <c r="M7" t="n">
-        <v>2.978087633010651</v>
+        <v>2.981561644778327</v>
       </c>
       <c r="N7" t="n">
-        <v>17.05159472561903</v>
+        <v>17.06139579834765</v>
       </c>
       <c r="O7" t="n">
-        <v>4.129357665015109</v>
+        <v>4.130544249653749</v>
       </c>
       <c r="P7" t="n">
-        <v>376.2220300229437</v>
+        <v>376.2394504019388</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25755,28 +25804,28 @@
         <v>0.1273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1814396168162645</v>
+        <v>0.1785733612416529</v>
       </c>
       <c r="J8" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K8" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07649164601750369</v>
+        <v>0.07422883488792897</v>
       </c>
       <c r="M8" t="n">
-        <v>3.887716276780156</v>
+        <v>3.894604749080395</v>
       </c>
       <c r="N8" t="n">
-        <v>24.34852593291164</v>
+        <v>24.41686960438648</v>
       </c>
       <c r="O8" t="n">
-        <v>4.934422553137463</v>
+        <v>4.941342894840074</v>
       </c>
       <c r="P8" t="n">
-        <v>378.5086056559221</v>
+        <v>378.5368826721557</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25833,28 +25882,28 @@
         <v>0.0502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06814798141575255</v>
+        <v>0.0663084358268009</v>
       </c>
       <c r="J9" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K9" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01440770584075357</v>
+        <v>0.0136741491940614</v>
       </c>
       <c r="M9" t="n">
-        <v>3.477773943396614</v>
+        <v>3.480379152944773</v>
       </c>
       <c r="N9" t="n">
-        <v>19.46211664146666</v>
+        <v>19.47077775847025</v>
       </c>
       <c r="O9" t="n">
-        <v>4.411588902137942</v>
+        <v>4.412570425326972</v>
       </c>
       <c r="P9" t="n">
-        <v>379.2069331169097</v>
+        <v>379.225081135859</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25911,28 +25960,28 @@
         <v>0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09321711027978943</v>
+        <v>0.09094045771437566</v>
       </c>
       <c r="J10" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K10" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04065534825754047</v>
+        <v>0.03870603687122487</v>
       </c>
       <c r="M10" t="n">
-        <v>2.884278869600076</v>
+        <v>2.890540136039811</v>
       </c>
       <c r="N10" t="n">
-        <v>12.5611631579243</v>
+        <v>12.61006751488445</v>
       </c>
       <c r="O10" t="n">
-        <v>3.544173127532613</v>
+        <v>3.551065687210594</v>
       </c>
       <c r="P10" t="n">
-        <v>384.1606870926161</v>
+        <v>384.1831473861506</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25970,7 +26019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K484"/>
+  <dimension ref="A1:K485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53561,6 +53610,63 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>-34.989045715663394,173.47984714492273</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>-34.989503551809605,173.480503749091</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>-34.98967249939593,173.48134881732582</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-34.98981034025459,173.48223199549295</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>-34.99002073856022,173.48309353347955</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>-34.99018085362305,173.48395593982562</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>-34.99028188295712,173.4848227528672</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>-34.99026768216632,173.4857191608149</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>-34.99031265979657,173.48661627086625</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0041/nzd0041.xlsx
+++ b/data/nzd0041/nzd0041.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K485"/>
+  <dimension ref="A1:K488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19361,6 +19361,123 @@
       <c r="K485" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>378.74</v>
+      </c>
+      <c r="C486" t="n">
+        <v>372.92</v>
+      </c>
+      <c r="D486" t="n">
+        <v>364.73</v>
+      </c>
+      <c r="E486" t="n">
+        <v>366.76</v>
+      </c>
+      <c r="F486" t="n">
+        <v>371.91</v>
+      </c>
+      <c r="G486" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="H486" t="n">
+        <v>376.15</v>
+      </c>
+      <c r="I486" t="n">
+        <v>376.92</v>
+      </c>
+      <c r="J486" t="n">
+        <v>380.96</v>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>376.62</v>
+      </c>
+      <c r="C487" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="D487" t="n">
+        <v>364.09</v>
+      </c>
+      <c r="E487" t="n">
+        <v>366.38</v>
+      </c>
+      <c r="F487" t="n">
+        <v>371.38</v>
+      </c>
+      <c r="G487" t="n">
+        <v>376.04</v>
+      </c>
+      <c r="H487" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="I487" t="n">
+        <v>376.51</v>
+      </c>
+      <c r="J487" t="n">
+        <v>380.93</v>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>382.16</v>
+      </c>
+      <c r="C488" t="n">
+        <v>372.84</v>
+      </c>
+      <c r="D488" t="n">
+        <v>365.82</v>
+      </c>
+      <c r="E488" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="F488" t="n">
+        <v>371.55</v>
+      </c>
+      <c r="G488" t="n">
+        <v>376.67</v>
+      </c>
+      <c r="H488" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="I488" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="J488" t="n">
+        <v>381.33</v>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19375,7 +19492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B579"/>
+  <dimension ref="A1:B582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25168,6 +25285,36 @@
       </c>
       <c r="B579" t="n">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -25336,28 +25483,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5236389880995698</v>
+        <v>0.5116218886683742</v>
       </c>
       <c r="J2" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K2" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1789981735538143</v>
+        <v>0.1727336830572991</v>
       </c>
       <c r="M2" t="n">
-        <v>6.772198383156253</v>
+        <v>6.78551810725827</v>
       </c>
       <c r="N2" t="n">
-        <v>77.21205385669964</v>
+        <v>77.46761036463879</v>
       </c>
       <c r="O2" t="n">
-        <v>8.787038969795208</v>
+        <v>8.801568630911127</v>
       </c>
       <c r="P2" t="n">
-        <v>375.9862944480294</v>
+        <v>376.1052700276959</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25414,28 +25561,28 @@
         <v>0.1183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.249068652317975</v>
+        <v>0.2464742722721966</v>
       </c>
       <c r="J3" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K3" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2439521253752939</v>
+        <v>0.241910892912059</v>
       </c>
       <c r="M3" t="n">
-        <v>2.685463413385588</v>
+        <v>2.68247939187364</v>
       </c>
       <c r="N3" t="n">
-        <v>11.80343638569793</v>
+        <v>11.76417931429482</v>
       </c>
       <c r="O3" t="n">
-        <v>3.435612956329325</v>
+        <v>3.429894942165842</v>
       </c>
       <c r="P3" t="n">
-        <v>368.3045322264322</v>
+        <v>368.3302244835571</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25492,28 +25639,28 @@
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2424592457364116</v>
+        <v>0.2389557944167455</v>
       </c>
       <c r="J4" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K4" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1878651317543121</v>
+        <v>0.1847659581253226</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05354725261306</v>
+        <v>3.054307907939698</v>
       </c>
       <c r="N4" t="n">
-        <v>15.60217362115848</v>
+        <v>15.56858341187172</v>
       </c>
       <c r="O4" t="n">
-        <v>3.949958686006536</v>
+        <v>3.945704425305034</v>
       </c>
       <c r="P4" t="n">
-        <v>361.5620361469078</v>
+        <v>361.5967213367646</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25570,28 +25717,28 @@
         <v>0.1474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.281279369126937</v>
+        <v>0.2773531083310062</v>
       </c>
       <c r="J5" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K5" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L5" t="n">
-        <v>0.27307205283892</v>
+        <v>0.268878805237855</v>
       </c>
       <c r="M5" t="n">
-        <v>2.81516338471639</v>
+        <v>2.81824013744735</v>
       </c>
       <c r="N5" t="n">
-        <v>12.930505421649</v>
+        <v>12.92565312361136</v>
       </c>
       <c r="O5" t="n">
-        <v>3.595901197425897</v>
+        <v>3.595226435652053</v>
       </c>
       <c r="P5" t="n">
-        <v>362.6701964051854</v>
+        <v>362.7090793114998</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25648,28 +25795,28 @@
         <v>0.1387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2383116614697237</v>
+        <v>0.2349413338687559</v>
       </c>
       <c r="J6" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K6" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L6" t="n">
-        <v>0.158654622373804</v>
+        <v>0.1561613659619333</v>
       </c>
       <c r="M6" t="n">
-        <v>3.282622914007482</v>
+        <v>3.279230411296481</v>
       </c>
       <c r="N6" t="n">
-        <v>18.49003799940491</v>
+        <v>18.43139828201742</v>
       </c>
       <c r="O6" t="n">
-        <v>4.300004418533184</v>
+        <v>4.293180439023897</v>
       </c>
       <c r="P6" t="n">
-        <v>368.2847931813058</v>
+        <v>368.3181736122103</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25726,28 +25873,28 @@
         <v>0.1225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.188462490367517</v>
+        <v>0.1830376868198414</v>
       </c>
       <c r="J7" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K7" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1133249214415187</v>
+        <v>0.1080003228829378</v>
       </c>
       <c r="M7" t="n">
-        <v>2.981561644778327</v>
+        <v>2.992710235894597</v>
       </c>
       <c r="N7" t="n">
-        <v>17.06139579834765</v>
+        <v>17.09914118722304</v>
       </c>
       <c r="O7" t="n">
-        <v>4.130544249653749</v>
+        <v>4.135110782944398</v>
       </c>
       <c r="P7" t="n">
-        <v>376.2394504019388</v>
+        <v>376.2931727914345</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25804,28 +25951,28 @@
         <v>0.1273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1785733612416529</v>
+        <v>0.1708577924390214</v>
       </c>
       <c r="J8" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K8" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07422883488792897</v>
+        <v>0.0684372992765534</v>
       </c>
       <c r="M8" t="n">
-        <v>3.894604749080395</v>
+        <v>3.910828609273447</v>
       </c>
       <c r="N8" t="n">
-        <v>24.41686960438648</v>
+        <v>24.55514074592259</v>
       </c>
       <c r="O8" t="n">
-        <v>4.941342894840074</v>
+        <v>4.95531439425619</v>
       </c>
       <c r="P8" t="n">
-        <v>378.5368826721557</v>
+        <v>378.6132886867703</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25882,28 +26029,28 @@
         <v>0.0502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0663084358268009</v>
+        <v>0.06151442043590134</v>
       </c>
       <c r="J9" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K9" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0136741491940614</v>
+        <v>0.01187213237718454</v>
       </c>
       <c r="M9" t="n">
-        <v>3.480379152944773</v>
+        <v>3.48412549524756</v>
       </c>
       <c r="N9" t="n">
-        <v>19.47077775847025</v>
+        <v>19.4621989647751</v>
       </c>
       <c r="O9" t="n">
-        <v>4.412570425326972</v>
+        <v>4.411598232474836</v>
       </c>
       <c r="P9" t="n">
-        <v>379.225081135859</v>
+        <v>379.272560318373</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25960,28 +26107,28 @@
         <v>0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09094045771437566</v>
+        <v>0.08475987235177075</v>
       </c>
       <c r="J10" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K10" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03870603687122487</v>
+        <v>0.03373122571208897</v>
       </c>
       <c r="M10" t="n">
-        <v>2.890540136039811</v>
+        <v>2.906146980164475</v>
       </c>
       <c r="N10" t="n">
-        <v>12.61006751488445</v>
+        <v>12.71744968806667</v>
       </c>
       <c r="O10" t="n">
-        <v>3.551065687210594</v>
+        <v>3.566153346123337</v>
       </c>
       <c r="P10" t="n">
-        <v>384.1831473861506</v>
+        <v>384.2443540608461</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26019,7 +26166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K485"/>
+  <dimension ref="A1:K488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53667,6 +53814,177 @@
         </is>
       </c>
     </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>-34.989034753955984,173.47985714297667</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>-34.98950255121084,173.48050424962062</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>-34.989672410593066,173.4813488363501</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-34.989810600231685,173.48223190463037</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>-34.990020481269795,173.48309363500795</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>-34.990181648499274,173.48395574094562</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>-34.99027801141602,173.48482301205715</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>-34.99026065669958,173.4857195677869</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>-34.990309434370495,173.4866167164662</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>-34.98905004265294,173.47984319832173</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>-34.98950955540219,173.48050074591305</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>-34.989678093976416,173.48134761879757</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-34.9898138932749,173.48223075370416</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>-34.99002502673384,173.4830918413392</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>-34.99018571119995,173.48395472444776</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>-34.99027765127266,173.48482303616782</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>-34.99026434957313,173.48571935386576</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>-34.990309703156,173.48661667933288</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-34.98901009011131,173.47987963858833</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-34.989503218276674,173.4805039159342</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-34.989662731080756,173.48135090999378</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-34.98981025359556,173.48223202578046</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-34.99002356875481,173.48309241666692</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>-34.99018014706642,173.48395611660786</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-34.990271888978924,173.48482342193887</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-34.99026281838166,173.48571944256477</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>-34.99030611934925,173.48661717444395</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0041/nzd0041.xlsx
+++ b/data/nzd0041/nzd0041.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K488"/>
+  <dimension ref="A1:K492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19476,6 +19476,162 @@
         <v>381.33</v>
       </c>
       <c r="K488" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>380.47</v>
+      </c>
+      <c r="C489" t="n">
+        <v>372.68</v>
+      </c>
+      <c r="D489" t="n">
+        <v>365.86</v>
+      </c>
+      <c r="E489" t="n">
+        <v>366.73</v>
+      </c>
+      <c r="F489" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="G489" t="n">
+        <v>376.57</v>
+      </c>
+      <c r="H489" t="n">
+        <v>376.85</v>
+      </c>
+      <c r="I489" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="J489" t="n">
+        <v>381.16</v>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="C490" t="n">
+        <v>372.33</v>
+      </c>
+      <c r="D490" t="n">
+        <v>365.76</v>
+      </c>
+      <c r="E490" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="F490" t="n">
+        <v>371.61</v>
+      </c>
+      <c r="G490" t="n">
+        <v>376.36</v>
+      </c>
+      <c r="H490" t="n">
+        <v>376.22</v>
+      </c>
+      <c r="I490" t="n">
+        <v>376.51</v>
+      </c>
+      <c r="J490" t="n">
+        <v>380.67</v>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>378.71</v>
+      </c>
+      <c r="C491" t="n">
+        <v>371.19</v>
+      </c>
+      <c r="D491" t="n">
+        <v>364.97</v>
+      </c>
+      <c r="E491" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="F491" t="n">
+        <v>371.55</v>
+      </c>
+      <c r="G491" t="n">
+        <v>377.77</v>
+      </c>
+      <c r="H491" t="n">
+        <v>376.74</v>
+      </c>
+      <c r="I491" t="n">
+        <v>376.1</v>
+      </c>
+      <c r="J491" t="n">
+        <v>380.44</v>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>378.15</v>
+      </c>
+      <c r="C492" t="n">
+        <v>371.15</v>
+      </c>
+      <c r="D492" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="E492" t="n">
+        <v>365.86</v>
+      </c>
+      <c r="F492" t="n">
+        <v>371.44</v>
+      </c>
+      <c r="G492" t="n">
+        <v>377.31</v>
+      </c>
+      <c r="H492" t="n">
+        <v>376.51</v>
+      </c>
+      <c r="I492" t="n">
+        <v>375.32</v>
+      </c>
+      <c r="J492" t="n">
+        <v>380.41</v>
+      </c>
+      <c r="K492" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19492,7 +19648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B582"/>
+  <dimension ref="A1:B586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25315,6 +25471,46 @@
       </c>
       <c r="B582" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -25483,28 +25679,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5116218886683742</v>
+        <v>0.4962470714146502</v>
       </c>
       <c r="J2" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K2" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1727336830572991</v>
+        <v>0.1649153442880262</v>
       </c>
       <c r="M2" t="n">
-        <v>6.78551810725827</v>
+        <v>6.802009909440385</v>
       </c>
       <c r="N2" t="n">
-        <v>77.46761036463879</v>
+        <v>77.71779462656953</v>
       </c>
       <c r="O2" t="n">
-        <v>8.801568630911127</v>
+        <v>8.815769655938698</v>
       </c>
       <c r="P2" t="n">
-        <v>376.1052700276959</v>
+        <v>376.2582272873792</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25561,28 +25757,28 @@
         <v>0.1183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2464742722721966</v>
+        <v>0.2419659449808663</v>
       </c>
       <c r="J3" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K3" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L3" t="n">
-        <v>0.241910892912059</v>
+        <v>0.2370005837677386</v>
       </c>
       <c r="M3" t="n">
-        <v>2.68247939187364</v>
+        <v>2.683959592133115</v>
       </c>
       <c r="N3" t="n">
-        <v>11.76417931429482</v>
+        <v>11.74730918239585</v>
       </c>
       <c r="O3" t="n">
-        <v>3.429894942165842</v>
+        <v>3.427434781640031</v>
       </c>
       <c r="P3" t="n">
-        <v>368.3302244835571</v>
+        <v>368.3750808543783</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25639,28 +25835,28 @@
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2389557944167455</v>
+        <v>0.2350446792628237</v>
       </c>
       <c r="J4" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K4" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1847659581253226</v>
+        <v>0.1817578100260805</v>
       </c>
       <c r="M4" t="n">
-        <v>3.054307907939698</v>
+        <v>3.051075927384061</v>
       </c>
       <c r="N4" t="n">
-        <v>15.56858341187172</v>
+        <v>15.5004659323689</v>
       </c>
       <c r="O4" t="n">
-        <v>3.945704425305034</v>
+        <v>3.937063110031245</v>
       </c>
       <c r="P4" t="n">
-        <v>361.5967213367646</v>
+        <v>361.6356350945651</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25717,28 +25913,28 @@
         <v>0.1474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2773531083310062</v>
+        <v>0.2716477984817119</v>
       </c>
       <c r="J5" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K5" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L5" t="n">
-        <v>0.268878805237855</v>
+        <v>0.2621903089922172</v>
       </c>
       <c r="M5" t="n">
-        <v>2.81824013744735</v>
+        <v>2.82589846274483</v>
       </c>
       <c r="N5" t="n">
-        <v>12.92565312361136</v>
+        <v>12.94181585275756</v>
       </c>
       <c r="O5" t="n">
-        <v>3.595226435652053</v>
+        <v>3.59747353746453</v>
       </c>
       <c r="P5" t="n">
-        <v>362.7090793114998</v>
+        <v>362.765838853475</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25795,28 +25991,28 @@
         <v>0.1387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2349413338687559</v>
+        <v>0.2305850368653764</v>
       </c>
       <c r="J6" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K6" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1561613659619333</v>
+        <v>0.1529502007543705</v>
       </c>
       <c r="M6" t="n">
-        <v>3.279230411296481</v>
+        <v>3.274365423356837</v>
       </c>
       <c r="N6" t="n">
-        <v>18.43139828201742</v>
+        <v>18.35169794106028</v>
       </c>
       <c r="O6" t="n">
-        <v>4.293180439023897</v>
+        <v>4.283888180270382</v>
       </c>
       <c r="P6" t="n">
-        <v>368.3181736122103</v>
+        <v>368.3615110392056</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25873,28 +26069,28 @@
         <v>0.1225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1830376868198414</v>
+        <v>0.1769137629723367</v>
       </c>
       <c r="J7" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K7" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1080003228829378</v>
+        <v>0.1023858875306127</v>
       </c>
       <c r="M7" t="n">
-        <v>2.992710235894597</v>
+        <v>3.002128759360683</v>
       </c>
       <c r="N7" t="n">
-        <v>17.09914118722304</v>
+        <v>17.10125289793771</v>
       </c>
       <c r="O7" t="n">
-        <v>4.135110782944398</v>
+        <v>4.135366114135206</v>
       </c>
       <c r="P7" t="n">
-        <v>376.2931727914345</v>
+        <v>376.3540865226458</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25951,28 +26147,28 @@
         <v>0.1273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1708577924390214</v>
+        <v>0.1611861267007242</v>
       </c>
       <c r="J8" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K8" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0684372992765534</v>
+        <v>0.06151898442550063</v>
       </c>
       <c r="M8" t="n">
-        <v>3.910828609273447</v>
+        <v>3.930547388810564</v>
       </c>
       <c r="N8" t="n">
-        <v>24.55514074592259</v>
+        <v>24.70169583089533</v>
       </c>
       <c r="O8" t="n">
-        <v>4.95531439425619</v>
+        <v>4.97008006282548</v>
       </c>
       <c r="P8" t="n">
-        <v>378.6132886867703</v>
+        <v>378.7095003025664</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26029,28 +26225,28 @@
         <v>0.0502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06151442043590134</v>
+        <v>0.05452931168204767</v>
       </c>
       <c r="J9" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K9" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01187213237718454</v>
+        <v>0.009420484201957069</v>
       </c>
       <c r="M9" t="n">
-        <v>3.48412549524756</v>
+        <v>3.491939449760828</v>
       </c>
       <c r="N9" t="n">
-        <v>19.4621989647751</v>
+        <v>19.4863843941011</v>
       </c>
       <c r="O9" t="n">
-        <v>4.411598232474836</v>
+        <v>4.414338500172036</v>
       </c>
       <c r="P9" t="n">
-        <v>379.272560318373</v>
+        <v>379.3420537299457</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26107,28 +26303,28 @@
         <v>0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08475987235177075</v>
+        <v>0.07620272970699331</v>
       </c>
       <c r="J10" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K10" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03373122571208897</v>
+        <v>0.02731905328408379</v>
       </c>
       <c r="M10" t="n">
-        <v>2.906146980164475</v>
+        <v>2.929607639176806</v>
       </c>
       <c r="N10" t="n">
-        <v>12.71744968806667</v>
+        <v>12.88548998574324</v>
       </c>
       <c r="O10" t="n">
-        <v>3.566153346123337</v>
+        <v>3.589636469859203</v>
       </c>
       <c r="P10" t="n">
-        <v>384.2443540608461</v>
+        <v>384.3294818092355</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26166,7 +26362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K488"/>
+  <dimension ref="A1:K492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53985,6 +54181,234 @@
         </is>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-34.98902227780115,173.47986852233745</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-34.98950455240838,173.48050324856138</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-34.9896623758693,173.4813509860908</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-34.98981086020878,173.48223181376778</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-34.99002056703327,173.48309360116517</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>-34.990181030262214,173.48395589563006</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>-34.990271708907244,173.4848234339942</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>-34.99026281838166,173.48571944256477</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-34.99030764246712,173.48661696402175</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-34.9890269653739,173.4798642468555</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-34.98950747082146,173.4805017886832</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-34.989663263897945,173.48135079584827</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-34.989813806615864,173.4822307839917</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-34.990023054173975,173.48309261972375</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-34.99018288497341,173.4839554315767</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-34.990277381165136,173.48482305425082</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-34.99026434957313,173.48571935386576</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-34.9903120326304,173.48661635751068</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-34.989034970305475,173.47985694564667</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-34.98951697650959,173.48049703365078</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-34.9896702793243,173.48134929293224</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-34.98981787959033,173.48222936047762</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-34.99002356875481,173.48309241666692</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-34.99017043191259,173.48395854736313</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-34.99027269930149,173.4848233676898</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-34.99026804244668,173.48571913994454</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-34.990314093319284,173.4866160728218</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-34.98903900882935,173.4798532621534</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-34.989517310042515,173.4804968668075</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-34.989673032213105,173.4813487031803</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-34.989818399544525,173.4822291787524</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-34.990024512153,173.48309204439602</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-34.990174494613285,173.48395753086552</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-34.990274770125794,173.48482322905335</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-34.99027506791341,173.48571873297251</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-34.990314362104776,173.48661603568846</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0041/nzd0041.xlsx
+++ b/data/nzd0041/nzd0041.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K492"/>
+  <dimension ref="A1:K496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19632,6 +19632,162 @@
         <v>380.41</v>
       </c>
       <c r="K492" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>374.93</v>
+      </c>
+      <c r="C493" t="n">
+        <v>369.51</v>
+      </c>
+      <c r="D493" t="n">
+        <v>364.17</v>
+      </c>
+      <c r="E493" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="F493" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="G493" t="n">
+        <v>377.6</v>
+      </c>
+      <c r="H493" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="I493" t="n">
+        <v>375.28</v>
+      </c>
+      <c r="J493" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>375.76</v>
+      </c>
+      <c r="C494" t="n">
+        <v>367.99</v>
+      </c>
+      <c r="D494" t="n">
+        <v>363.24</v>
+      </c>
+      <c r="E494" t="n">
+        <v>365.82</v>
+      </c>
+      <c r="F494" t="n">
+        <v>370.99</v>
+      </c>
+      <c r="G494" t="n">
+        <v>376.17</v>
+      </c>
+      <c r="H494" t="n">
+        <v>376.18</v>
+      </c>
+      <c r="I494" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="J494" t="n">
+        <v>380.34</v>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>378.67</v>
+      </c>
+      <c r="C495" t="n">
+        <v>368.63</v>
+      </c>
+      <c r="D495" t="n">
+        <v>364.18</v>
+      </c>
+      <c r="E495" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="F495" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="G495" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="H495" t="n">
+        <v>377.03</v>
+      </c>
+      <c r="I495" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="J495" t="n">
+        <v>381.24</v>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="C496" t="n">
+        <v>369.41</v>
+      </c>
+      <c r="D496" t="n">
+        <v>365.21</v>
+      </c>
+      <c r="E496" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="F496" t="n">
+        <v>371.76</v>
+      </c>
+      <c r="G496" t="n">
+        <v>378</v>
+      </c>
+      <c r="H496" t="n">
+        <v>377.59</v>
+      </c>
+      <c r="I496" t="n">
+        <v>375.27</v>
+      </c>
+      <c r="J496" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="K496" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19648,7 +19804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B586"/>
+  <dimension ref="A1:B591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25511,6 +25667,56 @@
       </c>
       <c r="B586" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -25679,28 +25885,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4962470714146502</v>
+        <v>0.478480911177651</v>
       </c>
       <c r="J2" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K2" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1649153442880262</v>
+        <v>0.1551961693815299</v>
       </c>
       <c r="M2" t="n">
-        <v>6.802009909440385</v>
+        <v>6.83145820638271</v>
       </c>
       <c r="N2" t="n">
-        <v>77.71779462656953</v>
+        <v>78.31866139473274</v>
       </c>
       <c r="O2" t="n">
-        <v>8.815769655938698</v>
+        <v>8.849783126988635</v>
       </c>
       <c r="P2" t="n">
-        <v>376.2582272873792</v>
+        <v>376.4356990028047</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25757,28 +25963,28 @@
         <v>0.1183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2419659449808663</v>
+        <v>0.2333518552838036</v>
       </c>
       <c r="J3" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K3" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2370005837677386</v>
+        <v>0.2227996122004603</v>
       </c>
       <c r="M3" t="n">
-        <v>2.683959592133115</v>
+        <v>2.70766108785667</v>
       </c>
       <c r="N3" t="n">
-        <v>11.74730918239585</v>
+        <v>11.93719368805734</v>
       </c>
       <c r="O3" t="n">
-        <v>3.427434781640031</v>
+        <v>3.455024412078349</v>
       </c>
       <c r="P3" t="n">
-        <v>368.3750808543783</v>
+        <v>368.4611456968228</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25835,28 +26041,28 @@
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2350446792628237</v>
+        <v>0.2296608343254532</v>
       </c>
       <c r="J4" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K4" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1817578100260805</v>
+        <v>0.1762743430269212</v>
       </c>
       <c r="M4" t="n">
-        <v>3.051075927384061</v>
+        <v>3.056511313589172</v>
       </c>
       <c r="N4" t="n">
-        <v>15.5004659323689</v>
+        <v>15.4891830185921</v>
       </c>
       <c r="O4" t="n">
-        <v>3.937063110031245</v>
+        <v>3.93562993923363</v>
       </c>
       <c r="P4" t="n">
-        <v>361.6356350945651</v>
+        <v>361.6894198458444</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25913,28 +26119,28 @@
         <v>0.1474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2716477984817119</v>
+        <v>0.2665099020001257</v>
       </c>
       <c r="J5" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K5" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2621903089922172</v>
+        <v>0.2564175939971574</v>
       </c>
       <c r="M5" t="n">
-        <v>2.82589846274483</v>
+        <v>2.831094358519489</v>
       </c>
       <c r="N5" t="n">
-        <v>12.94181585275756</v>
+        <v>12.94401864914501</v>
       </c>
       <c r="O5" t="n">
-        <v>3.59747353746453</v>
+        <v>3.597779683241458</v>
       </c>
       <c r="P5" t="n">
-        <v>362.765838853475</v>
+        <v>362.817157822125</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25991,28 +26197,28 @@
         <v>0.1387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2305850368653764</v>
+        <v>0.2258989766372944</v>
       </c>
       <c r="J6" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K6" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1529502007543705</v>
+        <v>0.1491986354405659</v>
       </c>
       <c r="M6" t="n">
-        <v>3.274365423356837</v>
+        <v>3.271621616090395</v>
       </c>
       <c r="N6" t="n">
-        <v>18.35169794106028</v>
+        <v>18.28744360832039</v>
       </c>
       <c r="O6" t="n">
-        <v>4.283888180270382</v>
+        <v>4.276382069965264</v>
       </c>
       <c r="P6" t="n">
-        <v>368.3615110392056</v>
+        <v>368.4083263599169</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26069,28 +26275,28 @@
         <v>0.1225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1769137629723367</v>
+        <v>0.1711869277505046</v>
       </c>
       <c r="J7" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K7" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1023858875306127</v>
+        <v>0.09726876830549391</v>
       </c>
       <c r="M7" t="n">
-        <v>3.002128759360683</v>
+        <v>3.01013653614933</v>
       </c>
       <c r="N7" t="n">
-        <v>17.10125289793771</v>
+        <v>17.09178390814932</v>
       </c>
       <c r="O7" t="n">
-        <v>4.135366114135206</v>
+        <v>4.134221076351545</v>
       </c>
       <c r="P7" t="n">
-        <v>376.3540865226458</v>
+        <v>376.4113025604857</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26147,28 +26353,28 @@
         <v>0.1273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1611861267007242</v>
+        <v>0.1520321390328856</v>
       </c>
       <c r="J8" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K8" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06151898442550063</v>
+        <v>0.05527946227937519</v>
       </c>
       <c r="M8" t="n">
-        <v>3.930547388810564</v>
+        <v>3.948511354321732</v>
       </c>
       <c r="N8" t="n">
-        <v>24.70169583089533</v>
+        <v>24.82398527839165</v>
       </c>
       <c r="O8" t="n">
-        <v>4.97008006282548</v>
+        <v>4.982367437111765</v>
       </c>
       <c r="P8" t="n">
-        <v>378.7095003025664</v>
+        <v>378.8009467598054</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26225,28 +26431,28 @@
         <v>0.0502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05452931168204767</v>
+        <v>0.04634292573554102</v>
       </c>
       <c r="J9" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K9" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009420484201957069</v>
+        <v>0.006844543789681024</v>
       </c>
       <c r="M9" t="n">
-        <v>3.491939449760828</v>
+        <v>3.507162991758038</v>
       </c>
       <c r="N9" t="n">
-        <v>19.4863843941011</v>
+        <v>19.58397154699123</v>
       </c>
       <c r="O9" t="n">
-        <v>4.414338500172036</v>
+        <v>4.425378124747221</v>
       </c>
       <c r="P9" t="n">
-        <v>379.3420537299457</v>
+        <v>379.4238434291582</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26303,28 +26509,28 @@
         <v>0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07620272970699331</v>
+        <v>0.06844447937711504</v>
       </c>
       <c r="J10" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K10" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02731905328408379</v>
+        <v>0.02212580007450282</v>
       </c>
       <c r="M10" t="n">
-        <v>2.929607639176806</v>
+        <v>2.949964711373867</v>
       </c>
       <c r="N10" t="n">
-        <v>12.88548998574324</v>
+        <v>13.01133920744488</v>
       </c>
       <c r="O10" t="n">
-        <v>3.589636469859203</v>
+        <v>3.607123397867736</v>
       </c>
       <c r="P10" t="n">
-        <v>384.3294818092355</v>
+        <v>384.406990843766</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26362,7 +26568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K492"/>
+  <dimension ref="A1:K496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54409,6 +54615,234 @@
         </is>
       </c>
     </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-34.98906223033945,173.47983208206008</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-34.98953098489178,173.4804900262326</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-34.98967738355349,173.48134777099165</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-34.989821519269654,173.48222808840106</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-34.990026484712864,173.4830912660114</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-34.99017193334545,173.483958171701</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-34.99028026231201,173.4848228613653</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-34.99027542819377,173.48571871210214</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-34.99030979275118,173.48661666695511</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-34.98905624467105,173.47983754152628</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-34.98954365914196,173.48048368618552</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-34.98968564221989,173.48134600173543</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-34.98981874618066,173.48222905760224</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-34.990028371509254,173.48309052146956</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-34.99018456304541,173.48395501171888</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-34.9902777413085,173.48482303014015</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-34.99028110260921,173.4857183833939</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-34.990314989270956,173.486615949044</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-34.98903525877147,173.47985668254003</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-34.98953832261561,173.48048635567926</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-34.989677294750635,173.48134779001592</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-34.98981025359556,173.48223202578046</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-34.99002657047633,173.4830912321686</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-34.9901797937881,173.48395620499895</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-34.99027008826214,173.4848235424923</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-34.99027524805359,173.4857187225373</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>-34.99030692570577,173.48661706304395</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-34.989028912519466,173.47986247088588</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-34.98953181872404,173.48048960912428</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-34.98966814805554,173.48134974951435</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-34.98980158769232,173.48223505453316</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-34.99002176772188,173.48309312736586</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-34.99016840056222,173.4839590556119</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-34.990265046255104,173.48482388004192</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-34.99027551826385,173.48571870688454</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-34.99030495461206,173.48661733535502</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
